--- a/data/trans_camb/P42-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P42-Edad-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,63</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,33</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16,63</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>-5,33</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,36; 21,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,33; 23,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,48; 3,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 21,29</t>
+          <t>8,36; 21,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 23,01</t>
+          <t>10,33; 23,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 3,41</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,13; 21,29</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 23,01</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-15,15; 3,41</t>
+          <t>-14,48; 3,54</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-12,24%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-12,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38,17%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>-12,24%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,15; 53,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,14; 58,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-31,85; 8,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 52,85</t>
+          <t>18,15; 53,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,23; 57,6</t>
+          <t>22,14; 58,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 8,26</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,34; 52,85</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21,23; 57,6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-33,68; 8,26</t>
+          <t>-31,85; 8,57</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-5,71</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>-5,71</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,93; 7,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,78; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,2; 3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,77</t>
+          <t>0,93; 7,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,73</t>
+          <t>-2,78; 4,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 3,47</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 7,77</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 4,73</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; 3,47</t>
+          <t>-12,2; 3,0</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-6,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>-6,48%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,05; 8,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,1; 5,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,73; 3,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,99</t>
+          <t>1,05; 8,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 5,46</t>
+          <t>-3,1; 5,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 4,03</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,02; 8,99</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 5,46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-13,5; 4,03</t>
+          <t>-13,73; 3,54</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,01</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>-2,67</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,8; 7,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,12; 4,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,92; 0,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,3</t>
+          <t>2,8; 7,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,96</t>
+          <t>-1,12; 4,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,92; 7,3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-1,08; 3,96</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 0,55</t>
+          <t>-5,92; 0,78</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-2,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>-2,87%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,95; 8,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,18; 4,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,3; 0,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,95</t>
+          <t>2,95; 8,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,33</t>
+          <t>-1,18; 4,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,57</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3,06; 7,95</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-1,13; 4,33</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-6,05; 0,57</t>
+          <t>-6,3; 0,84</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,94</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2,94</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,28; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,22; 5,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,27; 5,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,59</t>
+          <t>-0,28; 5,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,76</t>
+          <t>-0,22; 5,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 6,01</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-0,09; 5,59</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-0,02; 5,76</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0,35; 6,01</t>
+          <t>0,27; 5,93</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,3; 6,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,22; 6,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,28; 6,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,22</t>
+          <t>-0,3; 6,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,34</t>
+          <t>-0,22; 6,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,66</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-0,03; 6,22</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-0,02; 6,34</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 6,66</t>
+          <t>0,28; 6,51</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7,33</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7,29</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,84; 11,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,05; 11,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,62; 11,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,03</t>
+          <t>3,84; 11,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,47</t>
+          <t>3,05; 11,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,23</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4,06; 12,03</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>3,07; 11,47</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>3,62; 11,23</t>
+          <t>3,62; 11,39</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>8,46%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,4; 14,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,46; 13,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,04; 13,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,47</t>
+          <t>4,4; 14,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,79</t>
+          <t>3,46; 13,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,36</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,65; 14,47</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3,49; 13,79</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>4,13; 13,36</t>
+          <t>4,04; 13,79</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,39</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18,6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-18,6</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>12,39</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>-18,6</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,75; 14,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,83; 17,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-56,34; 18,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,94</t>
+          <t>2,75; 14,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,7; 18,42</t>
+          <t>6,83; 17,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 19,12</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,78; 14,94</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6,7; 18,42</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-54,23; 19,12</t>
+          <t>-56,34; 18,79</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-24,76%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-24,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>-24,76%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,45; 20,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,81; 24,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,51; 25,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,84; 21,15</t>
+          <t>3,45; 20,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,45; 25,81</t>
+          <t>8,81; 24,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 25,9</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>4,84; 21,15</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8,45; 25,81</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-70,91; 25,9</t>
+          <t>-72,51; 25,39</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,35</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20,32</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25,77</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>25,77</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>15,35</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20,32</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>25,77</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,58; 22,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,94; 27,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,96; 32,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,66; 22,88</t>
+          <t>7,58; 22,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,96; 27,85</t>
+          <t>12,94; 27,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,22; 32,51</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>8,66; 22,88</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>12,96; 27,85</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>19,22; 32,51</t>
+          <t>18,96; 32,32</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>45,16%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>35,61%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>45,16%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,63; 43,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,98; 53,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,33; 62,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,06; 43,07</t>
+          <t>12,63; 43,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,97; 52,77</t>
+          <t>20,98; 53,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,88; 63,48</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>14,06; 43,07</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>20,97; 52,77</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>30,88; 63,48</t>
+          <t>30,33; 62,54</t>
         </is>
       </c>
     </row>
@@ -2136,17 +1688,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,08</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2160,21 +1712,6 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>8,05</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>8,08</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
@@ -2189,47 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,18; 9,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,17; 9,88</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,73; 6,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,98</t>
+          <t>6,18; 9,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,93</t>
+          <t>6,17; 9,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 6,21</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>6,43; 9,98</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>6,4; 9,93</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-19,42; 6,21</t>
+          <t>-17,73; 6,29</t>
         </is>
       </c>
     </row>
@@ -2242,17 +1764,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,71%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,21 +1788,6 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-0,71%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>-0,71%</t>
         </is>
@@ -2295,47 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,63; 12,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,69; 12,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,6; 8,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,86</t>
+          <t>7,63; 12,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,81</t>
+          <t>7,69; 12,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 7,89</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>8,02; 12,86</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>8,01; 12,81</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>-24,65; 7,89</t>
+          <t>-22,6; 8,01</t>
         </is>
       </c>
     </row>
@@ -2347,14 +1839,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P42-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P42-Edad-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-4,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-4,86</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 21,35</t>
+          <t>7,85; 21,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 23,62</t>
+          <t>9,64; 23,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 3,54</t>
+          <t>-14,44; 3,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 21,35</t>
+          <t>7,85; 21,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 23,62</t>
+          <t>9,64; 23,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 3,54</t>
+          <t>-14,44; 3,88</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-12,24%</t>
+          <t>-11,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,24%</t>
+          <t>-11,15%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 53,93</t>
+          <t>16,75; 53,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 58,85</t>
+          <t>20,46; 58,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 8,57</t>
+          <t>-30,78; 9,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 53,93</t>
+          <t>16,75; 53,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 58,85</t>
+          <t>20,46; 58,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 8,57</t>
+          <t>-30,78; 9,58</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-9,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-9,72</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,43</t>
+          <t>0,93; 7,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,98</t>
+          <t>-2,39; 4,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 3,0</t>
+          <t>-14,92; -4,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,43</t>
+          <t>0,93; 7,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,98</t>
+          <t>-2,39; 4,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 3,0</t>
+          <t>-14,92; -4,96</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,48%</t>
+          <t>-11,03%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,48%</t>
+          <t>-11,03%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,62</t>
+          <t>1,06; 9,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,81</t>
+          <t>-2,64; 5,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 3,54</t>
+          <t>-17,07; -5,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,62</t>
+          <t>1,06; 9,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,81</t>
+          <t>-2,64; 5,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 3,54</t>
+          <t>-17,07; -5,72</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-3,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-3,16</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,46</t>
+          <t>2,88; 7,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,16</t>
+          <t>-0,91; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,78</t>
+          <t>-6,43; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,46</t>
+          <t>2,88; 7,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,16</t>
+          <t>-0,91; 4,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,78</t>
+          <t>-6,43; 0,0</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-3,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-3,39%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,2</t>
+          <t>3,02; 8,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,52</t>
+          <t>-0,97; 4,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,84</t>
+          <t>-6,88; -0,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,2</t>
+          <t>3,02; 8,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,52</t>
+          <t>-0,97; 4,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,84</t>
+          <t>-6,88; -0,01</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,47</t>
+          <t>-0,16; 5,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,78</t>
+          <t>-0,31; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,93</t>
+          <t>-0,17; 5,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,47</t>
+          <t>-0,16; 5,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,78</t>
+          <t>-0,31; 5,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,93</t>
+          <t>-0,17; 5,34</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,04</t>
+          <t>-0,18; 6,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 6,41</t>
+          <t>-0,3; 6,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,51</t>
+          <t>-0,18; 5,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,04</t>
+          <t>-0,18; 6,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 6,41</t>
+          <t>-0,3; 6,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,51</t>
+          <t>-0,18; 5,91</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>6,94</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,95</t>
+          <t>4,07; 12,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 11,35</t>
+          <t>3,49; 11,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,39</t>
+          <t>3,01; 10,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,95</t>
+          <t>4,07; 12,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 11,35</t>
+          <t>3,49; 11,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,39</t>
+          <t>3,01; 10,99</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,44</t>
+          <t>4,68; 15,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,6</t>
+          <t>3,95; 13,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,79</t>
+          <t>3,35; 13,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,44</t>
+          <t>4,68; 15,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,6</t>
+          <t>3,95; 13,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,79</t>
+          <t>3,35; 13,21</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-18,6</t>
+          <t>17,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-18,6</t>
+          <t>17,31</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,75; 14,64</t>
+          <t>3,42; 14,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,83; 17,59</t>
+          <t>6,36; 17,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 18,79</t>
+          <t>12,69; 22,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,75; 14,64</t>
+          <t>3,42; 14,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,83; 17,59</t>
+          <t>6,36; 17,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 18,79</t>
+          <t>12,69; 22,42</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-24,76%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-24,76%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,45; 20,6</t>
+          <t>4,6; 21,06</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,7</t>
+          <t>8,19; 24,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 25,39</t>
+          <t>16,17; 31,98</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,45; 20,6</t>
+          <t>4,6; 21,06</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,7</t>
+          <t>8,19; 24,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 25,39</t>
+          <t>16,17; 31,98</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25,77</t>
+          <t>25,94</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,77</t>
+          <t>25,94</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,58; 22,85</t>
+          <t>7,72; 22,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12,94; 27,5</t>
+          <t>12,43; 27,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,32</t>
+          <t>19,7; 32,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,58; 22,85</t>
+          <t>7,72; 22,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,94; 27,5</t>
+          <t>12,43; 27,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,32</t>
+          <t>19,7; 32,82</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,63; 43,75</t>
+          <t>12,15; 43,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20,98; 53,08</t>
+          <t>20,36; 52,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30,33; 62,54</t>
+          <t>31,37; 63,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,63; 43,75</t>
+          <t>12,15; 43,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,98; 53,08</t>
+          <t>20,36; 52,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,33; 62,54</t>
+          <t>31,37; 63,05</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,9</t>
+          <t>6,34; 9,88</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,88</t>
+          <t>6,38; 9,9</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,29</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,9</t>
+          <t>6,34; 9,88</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,88</t>
+          <t>6,38; 9,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,29</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,72</t>
+          <t>7,86; 12,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,62</t>
+          <t>7,94; 12,67</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 8,01</t>
+          <t>3,46; 8,63</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,72</t>
+          <t>7,86; 12,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,62</t>
+          <t>7,94; 12,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 8,01</t>
+          <t>3,46; 8,63</t>
         </is>
       </c>
     </row>
